--- a/Team_Tasks.xlsx
+++ b/Team_Tasks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\AHE_Group_E\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45185C6-ABBC-4E3E-9A26-CC573D6C8F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190F3378-F3AA-46D2-A606-E5C51D56E972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -43,16 +43,10 @@
     <t>Lab_1</t>
   </si>
   <si>
-    <t>Not Yet Done</t>
-  </si>
-  <si>
     <t>Completed the Lab Together Team Mates</t>
   </si>
   <si>
     <t>Lab_2</t>
-  </si>
-  <si>
-    <t>Not Done</t>
   </si>
   <si>
     <t>Lab_3</t>
@@ -64,13 +58,55 @@
     <t>Done</t>
   </si>
   <si>
-    <t xml:space="preserve">    Completed exercise 1 of the Lab Together Team Mates</t>
+    <t>Md Ruhul Kuddus Saleh</t>
   </si>
   <si>
-    <t>Exercise 1 Done</t>
+    <t>Lab_5</t>
   </si>
   <si>
-    <t>Md Ruhul Kuddus Saleh</t>
+    <t>Lab_6</t>
+  </si>
+  <si>
+    <t>Project_TMP3</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Project_OLEDrgb</t>
+  </si>
+  <si>
+    <t>Project_ESP32</t>
+  </si>
+  <si>
+    <t>Worked on Vivado and Vitis</t>
+  </si>
+  <si>
+    <t>Project_OnBoard_TMP</t>
+  </si>
+  <si>
+    <t>Final_Project</t>
+  </si>
+  <si>
+    <t>Integrated all PMODs, Components and Codes with Team Mates</t>
+  </si>
+  <si>
+    <t>Project_Proposal</t>
+  </si>
+  <si>
+    <t>Project_Report</t>
+  </si>
+  <si>
+    <t>Project_SysML_Diagram</t>
+  </si>
+  <si>
+    <t>Worked</t>
+  </si>
+  <si>
+    <t>Working</t>
+  </si>
+  <si>
+    <t>Updated</t>
   </si>
 </sst>
 </file>
@@ -150,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -225,11 +261,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -249,9 +365,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -261,6 +374,36 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,7 +624,7 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="36.6640625" customWidth="1"/>
     <col min="4" max="4" width="39.33203125" customWidth="1"/>
@@ -500,9 +643,9 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="5"/>
@@ -540,7 +683,7 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="9"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -567,15 +710,13 @@
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -601,17 +742,15 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="11"/>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -637,13 +776,15 @@
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="19"/>
       <c r="E5" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -669,17 +810,15 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -704,11 +843,17 @@
       <c r="Z6" s="5"/>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="C7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -732,11 +877,17 @@
       <c r="Z7" s="5"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="A8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -760,11 +911,17 @@
       <c r="Z8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="A9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -788,11 +945,17 @@
       <c r="Z9" s="5"/>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="A10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -816,11 +979,19 @@
       <c r="Z10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="A11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -844,11 +1015,17 @@
       <c r="Z11" s="5"/>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="A12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -872,11 +1049,17 @@
       <c r="Z12" s="5"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="A13" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -900,11 +1083,17 @@
       <c r="Z13" s="5"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="A14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -928,11 +1117,17 @@
       <c r="Z14" s="5"/>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="A15" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20" t="s">
+        <v>11</v>
+      </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -956,11 +1151,19 @@
       <c r="Z15" s="5"/>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="A16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>11</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -984,11 +1187,11 @@
       <c r="Z16" s="5"/>
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -1012,11 +1215,11 @@
       <c r="Z17" s="5"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -1040,11 +1243,11 @@
       <c r="Z18" s="5"/>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -1068,11 +1271,11 @@
       <c r="Z19" s="5"/>
     </row>
     <row r="20" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -1096,11 +1299,11 @@
       <c r="Z20" s="5"/>
     </row>
     <row r="21" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -1124,11 +1327,11 @@
       <c r="Z21" s="5"/>
     </row>
     <row r="22" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -1152,11 +1355,11 @@
       <c r="Z22" s="5"/>
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -1180,11 +1383,11 @@
       <c r="Z23" s="5"/>
     </row>
     <row r="24" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -1208,11 +1411,11 @@
       <c r="Z24" s="5"/>
     </row>
     <row r="25" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -1236,11 +1439,11 @@
       <c r="Z25" s="5"/>
     </row>
     <row r="26" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -1264,11 +1467,11 @@
       <c r="Z26" s="5"/>
     </row>
     <row r="27" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -1292,11 +1495,11 @@
       <c r="Z27" s="5"/>
     </row>
     <row r="28" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -1320,11 +1523,11 @@
       <c r="Z28" s="5"/>
     </row>
     <row r="29" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -28536,11 +28739,15 @@
       <c r="Z1000" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
